--- a/rtss-pre1917/src/main/resources/excel-templates/elementary-territory-1881-1913.xlsx
+++ b/rtss-pre1917/src/main/resources/excel-templates/elementary-territory-1881-1913.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\excel-templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7389FEBD-88E6-4C5C-BAC4-60873697DED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D47C7B3-177E-4246-9829-E62DEF7F974B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6075" yWindow="9600" windowWidth="28800" windowHeight="16905" xr2:uid="{BB18BFB1-C03A-41FE-BE1A-93D139757D6D}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{BB18BFB1-C03A-41FE-BE1A-93D139757D6D}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>XXX</t>
   </si>
@@ -106,6 +106,15 @@
   </si>
   <si>
     <t>еп</t>
+  </si>
+  <si>
+    <t>эмигр</t>
+  </si>
+  <si>
+    <t>иммигр</t>
+  </si>
+  <si>
+    <t>внутр. мигр</t>
   </si>
 </sst>
 </file>
@@ -189,7 +198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -215,6 +224,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4460,15 +4470,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>4762</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>14286</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>705802</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>18096</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>139</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4496,16 +4506,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>4762</xdr:colOff>
-      <xdr:row>92</xdr:row>
-      <xdr:rowOff>4761</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>694372</xdr:colOff>
+      <xdr:row>140</xdr:row>
+      <xdr:rowOff>8571</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>590550</xdr:colOff>
-      <xdr:row>137</xdr:row>
-      <xdr:rowOff>9524</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>628650</xdr:colOff>
+      <xdr:row>185</xdr:row>
+      <xdr:rowOff>19049</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4532,16 +4542,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>626745</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>277176</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>702945</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>162876</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>619125</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4886,17 +4896,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12B321D7-C433-4B50-AA6E-BF1C75F28F7F}">
-  <dimension ref="A1:I43"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:L43"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" customWidth="1"/>
-    <col min="4" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83984375" customWidth="1"/>
+    <col min="2" max="2" width="13.15625" customWidth="1"/>
+    <col min="3" max="3" width="15.578125" customWidth="1"/>
+    <col min="4" max="5" width="9.26171875" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="8.83984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="10.15625" customWidth="1"/>
+    <col min="12" max="12" width="11.734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="23.1" x14ac:dyDescent="0.85">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -4909,7 +4921,7 @@
       <c r="H1" s="7"/>
       <c r="I1" s="7"/>
     </row>
-    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -4922,7 +4934,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -4933,14 +4945,14 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="13"/>
+      <c r="C4" s="14"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -4948,7 +4960,7 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
-    <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2"/>
       <c r="B5" s="2" t="s">
         <v>3</v>
@@ -4974,8 +4986,17 @@
       <c r="I5" s="9" t="s">
         <v>14</v>
       </c>
+      <c r="J5" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="6" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="3">
         <v>1881</v>
       </c>
@@ -5007,8 +5028,11 @@
         <f>G6-H6</f>
         <v>19.801490062127176</v>
       </c>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
     </row>
-    <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="3">
         <f>A6+1</f>
         <v>1882</v>
@@ -5045,8 +5069,11 @@
         <f t="shared" ref="I7:I38" si="3">G7-H7</f>
         <v>19.415967691829763</v>
       </c>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
     </row>
-    <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="3">
         <f t="shared" ref="A8:A38" si="4">A7+1</f>
         <v>1883</v>
@@ -5083,8 +5110,11 @@
         <f t="shared" si="3"/>
         <v>19.04498902532508</v>
       </c>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
     </row>
-    <row r="9" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="3">
         <f t="shared" si="4"/>
         <v>1884</v>
@@ -5121,8 +5151,11 @@
         <f t="shared" si="3"/>
         <v>18.687746444656238</v>
       </c>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
     </row>
-    <row r="10" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="3">
         <f t="shared" si="4"/>
         <v>1885</v>
@@ -5159,8 +5192,11 @@
         <f t="shared" si="3"/>
         <v>18.343491041497558</v>
       </c>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
     </row>
-    <row r="11" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="3">
         <f t="shared" si="4"/>
         <v>1886</v>
@@ -5197,8 +5233,11 @@
         <f t="shared" si="3"/>
         <v>18.01152737752161</v>
       </c>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
     </row>
-    <row r="12" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="3">
         <f t="shared" si="4"/>
         <v>1887</v>
@@ -5235,8 +5274,11 @@
         <f t="shared" si="3"/>
         <v>17.691208796069017</v>
       </c>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="13"/>
     </row>
-    <row r="13" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="3">
         <f t="shared" si="4"/>
         <v>1888</v>
@@ -5273,8 +5315,11 @@
         <f t="shared" si="3"/>
         <v>17.38193321861257</v>
       </c>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
     </row>
-    <row r="14" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="3">
         <f t="shared" si="4"/>
         <v>1889</v>
@@ -5311,8 +5356,11 @@
         <f t="shared" si="3"/>
         <v>17.083139368521753</v>
       </c>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="13"/>
     </row>
-    <row r="15" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="3">
         <f t="shared" si="4"/>
         <v>1890</v>
@@ -5349,8 +5397,11 @@
         <f t="shared" si="3"/>
         <v>16.794303372296117</v>
       </c>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="13"/>
     </row>
-    <row r="16" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="3">
         <f t="shared" si="4"/>
         <v>1891</v>
@@ -5387,8 +5438,11 @@
         <f t="shared" si="3"/>
         <v>16.514935694969136</v>
       </c>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="13"/>
     </row>
-    <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="3">
         <f t="shared" si="4"/>
         <v>1892</v>
@@ -5425,8 +5479,11 @@
         <f t="shared" si="3"/>
         <v>16.244578371968352</v>
       </c>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
     </row>
-    <row r="18" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="3">
         <f t="shared" si="4"/>
         <v>1893</v>
@@ -5463,8 +5520,11 @@
         <f t="shared" si="3"/>
         <v>15.982802504505155</v>
       </c>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
     </row>
-    <row r="19" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="3">
         <f t="shared" si="4"/>
         <v>1894</v>
@@ -5501,8 +5561,11 @@
         <f t="shared" si="3"/>
         <v>15.729205989681645</v>
       </c>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="13"/>
     </row>
-    <row r="20" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="3">
         <f t="shared" si="4"/>
         <v>1895</v>
@@ -5539,8 +5602,11 @@
         <f t="shared" si="3"/>
         <v>15.483411460046998</v>
       </c>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
     </row>
-    <row r="21" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="3">
         <f t="shared" si="4"/>
         <v>1896</v>
@@ -5577,8 +5643,11 @@
         <f t="shared" si="3"/>
         <v>15.245064410397131</v>
       </c>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="13"/>
     </row>
-    <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="3">
         <f t="shared" si="4"/>
         <v>1897</v>
@@ -5615,8 +5684,11 @@
         <f t="shared" si="3"/>
         <v>15.013831492262245</v>
       </c>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="13"/>
     </row>
-    <row r="23" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="3">
         <f t="shared" si="4"/>
         <v>1898</v>
@@ -5653,8 +5725,11 @@
         <f t="shared" si="3"/>
         <v>14.789398958826315</v>
       </c>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="13"/>
     </row>
-    <row r="24" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="3">
         <f t="shared" si="4"/>
         <v>1899</v>
@@ -5691,8 +5766,11 @@
         <f t="shared" si="3"/>
         <v>14.571471245022931</v>
       </c>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="13"/>
     </row>
-    <row r="25" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="3">
         <f t="shared" si="4"/>
         <v>1900</v>
@@ -5729,8 +5807,11 @@
         <f t="shared" si="3"/>
         <v>14.359769669294504</v>
       </c>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+      <c r="L25" s="13"/>
     </row>
-    <row r="26" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="3">
         <f t="shared" si="4"/>
         <v>1901</v>
@@ -5767,8 +5848,11 @@
         <f t="shared" si="3"/>
         <v>14.154031245023972</v>
       </c>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="13"/>
     </row>
-    <row r="27" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="3">
         <f t="shared" si="4"/>
         <v>1902</v>
@@ -5805,8 +5889,11 @@
         <f t="shared" si="3"/>
         <v>13.95400759098013</v>
       </c>
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
+      <c r="L27" s="13"/>
     </row>
-    <row r="28" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="3">
         <f t="shared" si="4"/>
         <v>1903</v>
@@ -5843,8 +5930,11 @@
         <f t="shared" si="3"/>
         <v>13.759463931285243</v>
       </c>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+      <c r="L28" s="13"/>
     </row>
-    <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="3">
         <f t="shared" si="4"/>
         <v>1904</v>
@@ -5881,8 +5971,11 @@
         <f t="shared" si="3"/>
         <v>13.570178176439455</v>
       </c>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="13"/>
     </row>
-    <row r="30" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="3">
         <f t="shared" si="4"/>
         <v>1905</v>
@@ -5919,8 +6012,11 @@
         <f t="shared" si="3"/>
         <v>13.385940077839233</v>
       </c>
+      <c r="J30" s="13"/>
+      <c r="K30" s="13"/>
+      <c r="L30" s="13"/>
     </row>
-    <row r="31" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="3">
         <f t="shared" si="4"/>
         <v>1906</v>
@@ -5957,8 +6053,11 @@
         <f t="shared" si="3"/>
         <v>13.206550449022718</v>
       </c>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="13"/>
     </row>
-    <row r="32" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="3">
         <f t="shared" si="4"/>
         <v>1907</v>
@@ -5995,8 +6094,11 @@
         <f t="shared" si="3"/>
         <v>13.031820447577875</v>
       </c>
+      <c r="J32" s="13"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="13"/>
     </row>
-    <row r="33" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="3">
         <f t="shared" si="4"/>
         <v>1908</v>
@@ -6033,8 +6135,11 @@
         <f t="shared" si="3"/>
         <v>12.861570912271226</v>
       </c>
+      <c r="J33" s="13"/>
+      <c r="K33" s="13"/>
+      <c r="L33" s="13"/>
     </row>
-    <row r="34" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="3">
         <f t="shared" si="4"/>
         <v>1909</v>
@@ -6071,8 +6176,11 @@
         <f t="shared" si="3"/>
         <v>12.695631750505445</v>
       </c>
+      <c r="J34" s="13"/>
+      <c r="K34" s="13"/>
+      <c r="L34" s="13"/>
     </row>
-    <row r="35" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="3">
         <f t="shared" si="4"/>
         <v>1910</v>
@@ -6109,8 +6217,11 @@
         <f t="shared" si="3"/>
         <v>12.533841371703598</v>
       </c>
+      <c r="J35" s="13"/>
+      <c r="K35" s="13"/>
+      <c r="L35" s="13"/>
     </row>
-    <row r="36" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="3">
         <f t="shared" si="4"/>
         <v>1911</v>
@@ -6147,8 +6258,11 @@
         <f t="shared" si="3"/>
         <v>12.376046162652191</v>
       </c>
+      <c r="J36" s="13"/>
+      <c r="K36" s="13"/>
+      <c r="L36" s="13"/>
     </row>
-    <row r="37" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="3">
         <f t="shared" si="4"/>
         <v>1912</v>
@@ -6185,8 +6299,11 @@
         <f t="shared" si="3"/>
         <v>12.222100001222209</v>
       </c>
+      <c r="J37" s="13"/>
+      <c r="K37" s="13"/>
+      <c r="L37" s="13"/>
     </row>
-    <row r="38" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="3">
         <f t="shared" si="4"/>
         <v>1913</v>
@@ -6223,8 +6340,11 @@
         <f t="shared" si="3"/>
         <v>12.07186380523255</v>
       </c>
+      <c r="J38" s="13"/>
+      <c r="K38" s="13"/>
+      <c r="L38" s="13"/>
     </row>
-    <row r="39" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="3">
         <f>A38+1</f>
         <v>1914</v>
@@ -6240,8 +6360,11 @@
       <c r="G39" s="6"/>
       <c r="H39" s="6"/>
       <c r="I39" s="6"/>
+      <c r="J39" s="13"/>
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
     </row>
-    <row r="40" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="3"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -6251,8 +6374,11 @@
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
+      <c r="J40" s="13"/>
+      <c r="K40" s="13"/>
+      <c r="L40" s="13"/>
     </row>
-    <row r="41" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A41" s="10" t="s">
         <v>11</v>
       </c>
@@ -6282,8 +6408,20 @@
         <f>AVERAGE(I6:I20)</f>
         <v>17.480715361308548</v>
       </c>
+      <c r="J41" s="11" cm="1">
+        <f t="array" ref="J41">SUM(J6+J6:J20)</f>
+        <v>0</v>
+      </c>
+      <c r="K41" s="11" cm="1">
+        <f t="array" ref="K41">SUM(K6+K6:K20)</f>
+        <v>0</v>
+      </c>
+      <c r="L41" s="11" cm="1">
+        <f t="array" ref="L41">SUM(L6+L6:L20)</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A42" s="10" t="s">
         <v>12</v>
       </c>
@@ -6313,8 +6451,20 @@
         <f>AVERAGE(I21:I38)</f>
         <v>13.544587872086607</v>
       </c>
+      <c r="J42" s="11">
+        <f>SUM(J21:J39)</f>
+        <v>0</v>
+      </c>
+      <c r="K42" s="11">
+        <f>SUM(K21:K39)</f>
+        <v>0</v>
+      </c>
+      <c r="L42" s="11">
+        <f>SUM(L21:L39)</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A43" s="10" t="s">
         <v>13</v>
       </c>
@@ -6343,6 +6493,18 @@
       <c r="I43" s="12">
         <f>AVERAGE(I6:I38)</f>
         <v>15.333736730823857</v>
+      </c>
+      <c r="J43" s="11">
+        <f>J41+J42</f>
+        <v>0</v>
+      </c>
+      <c r="K43" s="11">
+        <f>K41+K42</f>
+        <v>0</v>
+      </c>
+      <c r="L43" s="11">
+        <f>L41+L42</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/rtss-pre1917/src/main/resources/excel-templates/elementary-territory-1881-1913.xlsx
+++ b/rtss-pre1917/src/main/resources/excel-templates/elementary-territory-1881-1913.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\excel-templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D47C7B3-177E-4246-9829-E62DEF7F974B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD7041A1-247D-4708-ABE1-0BA194E2A85F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{BB18BFB1-C03A-41FE-BE1A-93D139757D6D}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{BB18BFB1-C03A-41FE-BE1A-93D139757D6D}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>XXX</t>
   </si>
@@ -116,6 +116,18 @@
   <si>
     <t>внутр. мигр</t>
   </si>
+  <si>
+    <t>ест.</t>
+  </si>
+  <si>
+    <t>ест. + мех.</t>
+  </si>
+  <si>
+    <t>прирост населения</t>
+  </si>
+  <si>
+    <t>verify</t>
+  </si>
 </sst>
 </file>
 
@@ -124,7 +136,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -158,6 +170,14 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -198,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -225,8 +245,17 @@
     <xf numFmtId="3" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4896,7 +4925,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12B321D7-C433-4B50-AA6E-BF1C75F28F7F}">
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:Q43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="9.83984375" customWidth="1"/>
@@ -4906,9 +4935,12 @@
     <col min="6" max="9" width="8.83984375" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="10.15625" customWidth="1"/>
     <col min="12" max="12" width="11.734375" customWidth="1"/>
+    <col min="14" max="14" width="12.68359375" customWidth="1"/>
+    <col min="15" max="15" width="13.83984375" customWidth="1"/>
+    <col min="16" max="16" width="10.578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="23.1" x14ac:dyDescent="0.85">
+    <row r="1" spans="1:17" ht="23.1" x14ac:dyDescent="0.85">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -4921,7 +4953,7 @@
       <c r="H1" s="7"/>
       <c r="I1" s="7"/>
     </row>
-    <row r="2" spans="1:12" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:17" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -4934,7 +4966,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:12" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:17" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -4945,22 +4977,27 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:17" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="14"/>
+      <c r="C4" s="16"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
+      <c r="N4" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="O4" s="17"/>
+      <c r="P4" s="15"/>
     </row>
-    <row r="5" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:17" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2"/>
       <c r="B5" s="2" t="s">
         <v>3</v>
@@ -4995,8 +5032,17 @@
       <c r="L5" s="9" t="s">
         <v>17</v>
       </c>
+      <c r="N5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q5" s="14" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="6" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:17" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="3">
         <v>1881</v>
       </c>
@@ -5031,8 +5077,20 @@
       <c r="J6" s="13"/>
       <c r="K6" s="13"/>
       <c r="L6" s="13"/>
+      <c r="N6" s="13">
+        <f>D6-E6</f>
+        <v>20000</v>
+      </c>
+      <c r="O6" s="13">
+        <f>N6+F6</f>
+        <v>20050</v>
+      </c>
+      <c r="Q6" s="13">
+        <f>B7-B6-O6</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:17" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="3">
         <f>A6+1</f>
         <v>1882</v>
@@ -5072,14 +5130,26 @@
       <c r="J7" s="13"/>
       <c r="K7" s="13"/>
       <c r="L7" s="13"/>
+      <c r="N7" s="13">
+        <f t="shared" ref="N7:N38" si="4">D7-E7</f>
+        <v>20000</v>
+      </c>
+      <c r="O7" s="13">
+        <f t="shared" ref="O7:O38" si="5">N7+F7</f>
+        <v>20060</v>
+      </c>
+      <c r="Q7" s="13">
+        <f t="shared" ref="Q7:Q38" si="6">B8-B7-O7</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:17" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="3">
-        <f t="shared" ref="A8:A38" si="4">A7+1</f>
+        <f t="shared" ref="A8:A38" si="7">A7+1</f>
         <v>1883</v>
       </c>
       <c r="B8" s="5">
-        <f t="shared" ref="B8:B39" si="5">B7+D7-E7+F7</f>
+        <f t="shared" ref="B8:B39" si="8">B7+D7-E7+F7</f>
         <v>1040110</v>
       </c>
       <c r="C8" s="5">
@@ -5087,15 +5157,15 @@
         <v>1050145</v>
       </c>
       <c r="D8" s="5">
-        <f t="shared" ref="D8:D38" si="6">D7+100</f>
+        <f t="shared" ref="D8:D38" si="9">D7+100</f>
         <v>50200</v>
       </c>
       <c r="E8" s="5">
-        <f t="shared" ref="E8:E38" si="7">E7+100</f>
+        <f t="shared" ref="E8:E38" si="10">E7+100</f>
         <v>30200</v>
       </c>
       <c r="F8" s="5">
-        <f t="shared" ref="F8:F38" si="8">F7+10</f>
+        <f t="shared" ref="F8:F38" si="11">F7+10</f>
         <v>70</v>
       </c>
       <c r="G8" s="6">
@@ -5113,14 +5183,26 @@
       <c r="J8" s="13"/>
       <c r="K8" s="13"/>
       <c r="L8" s="13"/>
+      <c r="N8" s="13">
+        <f t="shared" si="4"/>
+        <v>20000</v>
+      </c>
+      <c r="O8" s="13">
+        <f t="shared" si="5"/>
+        <v>20070</v>
+      </c>
+      <c r="Q8" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:17" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1884</v>
       </c>
       <c r="B9" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1060180</v>
       </c>
       <c r="C9" s="5">
@@ -5128,15 +5210,15 @@
         <v>1070220</v>
       </c>
       <c r="D9" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>50300</v>
       </c>
       <c r="E9" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>30300</v>
       </c>
       <c r="F9" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>80</v>
       </c>
       <c r="G9" s="6">
@@ -5154,14 +5236,26 @@
       <c r="J9" s="13"/>
       <c r="K9" s="13"/>
       <c r="L9" s="13"/>
+      <c r="N9" s="13">
+        <f t="shared" si="4"/>
+        <v>20000</v>
+      </c>
+      <c r="O9" s="13">
+        <f t="shared" si="5"/>
+        <v>20080</v>
+      </c>
+      <c r="Q9" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:17" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1885</v>
       </c>
       <c r="B10" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1080260</v>
       </c>
       <c r="C10" s="5">
@@ -5169,15 +5263,15 @@
         <v>1090305</v>
       </c>
       <c r="D10" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>50400</v>
       </c>
       <c r="E10" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>30400</v>
       </c>
       <c r="F10" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>90</v>
       </c>
       <c r="G10" s="6">
@@ -5195,14 +5289,26 @@
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
       <c r="L10" s="13"/>
+      <c r="N10" s="13">
+        <f t="shared" si="4"/>
+        <v>20000</v>
+      </c>
+      <c r="O10" s="13">
+        <f t="shared" si="5"/>
+        <v>20090</v>
+      </c>
+      <c r="Q10" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:17" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1886</v>
       </c>
       <c r="B11" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1100350</v>
       </c>
       <c r="C11" s="5">
@@ -5210,15 +5316,15 @@
         <v>1110400</v>
       </c>
       <c r="D11" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>50500</v>
       </c>
       <c r="E11" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>30500</v>
       </c>
       <c r="F11" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>100</v>
       </c>
       <c r="G11" s="6">
@@ -5236,14 +5342,26 @@
       <c r="J11" s="13"/>
       <c r="K11" s="13"/>
       <c r="L11" s="13"/>
+      <c r="N11" s="13">
+        <f t="shared" si="4"/>
+        <v>20000</v>
+      </c>
+      <c r="O11" s="13">
+        <f t="shared" si="5"/>
+        <v>20100</v>
+      </c>
+      <c r="Q11" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:17" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1887</v>
       </c>
       <c r="B12" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1120450</v>
       </c>
       <c r="C12" s="5">
@@ -5251,15 +5369,15 @@
         <v>1130505</v>
       </c>
       <c r="D12" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>50600</v>
       </c>
       <c r="E12" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>30600</v>
       </c>
       <c r="F12" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>110</v>
       </c>
       <c r="G12" s="6">
@@ -5277,14 +5395,26 @@
       <c r="J12" s="13"/>
       <c r="K12" s="13"/>
       <c r="L12" s="13"/>
+      <c r="N12" s="13">
+        <f t="shared" si="4"/>
+        <v>20000</v>
+      </c>
+      <c r="O12" s="13">
+        <f t="shared" si="5"/>
+        <v>20110</v>
+      </c>
+      <c r="Q12" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:17" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1888</v>
       </c>
       <c r="B13" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1140560</v>
       </c>
       <c r="C13" s="5">
@@ -5292,15 +5422,15 @@
         <v>1150620</v>
       </c>
       <c r="D13" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>50700</v>
       </c>
       <c r="E13" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>30700</v>
       </c>
       <c r="F13" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>120</v>
       </c>
       <c r="G13" s="6">
@@ -5318,14 +5448,26 @@
       <c r="J13" s="13"/>
       <c r="K13" s="13"/>
       <c r="L13" s="13"/>
+      <c r="N13" s="13">
+        <f t="shared" si="4"/>
+        <v>20000</v>
+      </c>
+      <c r="O13" s="13">
+        <f t="shared" si="5"/>
+        <v>20120</v>
+      </c>
+      <c r="Q13" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:17" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1889</v>
       </c>
       <c r="B14" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1160680</v>
       </c>
       <c r="C14" s="5">
@@ -5333,15 +5475,15 @@
         <v>1170745</v>
       </c>
       <c r="D14" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>50800</v>
       </c>
       <c r="E14" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>30800</v>
       </c>
       <c r="F14" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>130</v>
       </c>
       <c r="G14" s="6">
@@ -5359,14 +5501,26 @@
       <c r="J14" s="13"/>
       <c r="K14" s="13"/>
       <c r="L14" s="13"/>
+      <c r="N14" s="13">
+        <f t="shared" si="4"/>
+        <v>20000</v>
+      </c>
+      <c r="O14" s="13">
+        <f t="shared" si="5"/>
+        <v>20130</v>
+      </c>
+      <c r="Q14" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:17" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1890</v>
       </c>
       <c r="B15" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1180810</v>
       </c>
       <c r="C15" s="5">
@@ -5374,15 +5528,15 @@
         <v>1190880</v>
       </c>
       <c r="D15" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>50900</v>
       </c>
       <c r="E15" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>30900</v>
       </c>
       <c r="F15" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>140</v>
       </c>
       <c r="G15" s="6">
@@ -5400,14 +5554,26 @@
       <c r="J15" s="13"/>
       <c r="K15" s="13"/>
       <c r="L15" s="13"/>
+      <c r="N15" s="13">
+        <f t="shared" si="4"/>
+        <v>20000</v>
+      </c>
+      <c r="O15" s="13">
+        <f t="shared" si="5"/>
+        <v>20140</v>
+      </c>
+      <c r="Q15" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:17" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1891</v>
       </c>
       <c r="B16" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1200950</v>
       </c>
       <c r="C16" s="5">
@@ -5415,15 +5581,15 @@
         <v>1211025</v>
       </c>
       <c r="D16" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>51000</v>
       </c>
       <c r="E16" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>31000</v>
       </c>
       <c r="F16" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>150</v>
       </c>
       <c r="G16" s="6">
@@ -5441,14 +5607,26 @@
       <c r="J16" s="13"/>
       <c r="K16" s="13"/>
       <c r="L16" s="13"/>
+      <c r="N16" s="13">
+        <f t="shared" si="4"/>
+        <v>20000</v>
+      </c>
+      <c r="O16" s="13">
+        <f t="shared" si="5"/>
+        <v>20150</v>
+      </c>
+      <c r="Q16" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:17" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1892</v>
       </c>
       <c r="B17" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1221100</v>
       </c>
       <c r="C17" s="5">
@@ -5456,15 +5634,15 @@
         <v>1231180</v>
       </c>
       <c r="D17" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>51100</v>
       </c>
       <c r="E17" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>31100</v>
       </c>
       <c r="F17" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>160</v>
       </c>
       <c r="G17" s="6">
@@ -5482,14 +5660,26 @@
       <c r="J17" s="13"/>
       <c r="K17" s="13"/>
       <c r="L17" s="13"/>
+      <c r="N17" s="13">
+        <f t="shared" si="4"/>
+        <v>20000</v>
+      </c>
+      <c r="O17" s="13">
+        <f t="shared" si="5"/>
+        <v>20160</v>
+      </c>
+      <c r="Q17" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:17" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1893</v>
       </c>
       <c r="B18" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1241260</v>
       </c>
       <c r="C18" s="5">
@@ -5497,15 +5687,15 @@
         <v>1251345</v>
       </c>
       <c r="D18" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>51200</v>
       </c>
       <c r="E18" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>31200</v>
       </c>
       <c r="F18" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>170</v>
       </c>
       <c r="G18" s="6">
@@ -5523,14 +5713,26 @@
       <c r="J18" s="13"/>
       <c r="K18" s="13"/>
       <c r="L18" s="13"/>
+      <c r="N18" s="13">
+        <f t="shared" si="4"/>
+        <v>20000</v>
+      </c>
+      <c r="O18" s="13">
+        <f t="shared" si="5"/>
+        <v>20170</v>
+      </c>
+      <c r="Q18" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="19" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:17" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1894</v>
       </c>
       <c r="B19" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1261430</v>
       </c>
       <c r="C19" s="5">
@@ -5538,15 +5740,15 @@
         <v>1271520</v>
       </c>
       <c r="D19" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>51300</v>
       </c>
       <c r="E19" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>31300</v>
       </c>
       <c r="F19" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>180</v>
       </c>
       <c r="G19" s="6">
@@ -5564,14 +5766,26 @@
       <c r="J19" s="13"/>
       <c r="K19" s="13"/>
       <c r="L19" s="13"/>
+      <c r="N19" s="13">
+        <f t="shared" si="4"/>
+        <v>20000</v>
+      </c>
+      <c r="O19" s="13">
+        <f t="shared" si="5"/>
+        <v>20180</v>
+      </c>
+      <c r="Q19" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="20" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:17" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1895</v>
       </c>
       <c r="B20" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1281610</v>
       </c>
       <c r="C20" s="5">
@@ -5579,15 +5793,15 @@
         <v>1291705</v>
       </c>
       <c r="D20" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>51400</v>
       </c>
       <c r="E20" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>31400</v>
       </c>
       <c r="F20" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>190</v>
       </c>
       <c r="G20" s="6">
@@ -5605,14 +5819,26 @@
       <c r="J20" s="13"/>
       <c r="K20" s="13"/>
       <c r="L20" s="13"/>
+      <c r="N20" s="13">
+        <f t="shared" si="4"/>
+        <v>20000</v>
+      </c>
+      <c r="O20" s="13">
+        <f t="shared" si="5"/>
+        <v>20190</v>
+      </c>
+      <c r="Q20" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:17" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1896</v>
       </c>
       <c r="B21" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1301800</v>
       </c>
       <c r="C21" s="5">
@@ -5620,15 +5846,15 @@
         <v>1311900</v>
       </c>
       <c r="D21" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>51500</v>
       </c>
       <c r="E21" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>31500</v>
       </c>
       <c r="F21" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>200</v>
       </c>
       <c r="G21" s="6">
@@ -5646,14 +5872,26 @@
       <c r="J21" s="13"/>
       <c r="K21" s="13"/>
       <c r="L21" s="13"/>
+      <c r="N21" s="13">
+        <f t="shared" si="4"/>
+        <v>20000</v>
+      </c>
+      <c r="O21" s="13">
+        <f t="shared" si="5"/>
+        <v>20200</v>
+      </c>
+      <c r="Q21" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="22" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:17" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1897</v>
       </c>
       <c r="B22" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1322000</v>
       </c>
       <c r="C22" s="5">
@@ -5661,15 +5899,15 @@
         <v>1332105</v>
       </c>
       <c r="D22" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>51600</v>
       </c>
       <c r="E22" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>31600</v>
       </c>
       <c r="F22" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>210</v>
       </c>
       <c r="G22" s="6">
@@ -5687,14 +5925,26 @@
       <c r="J22" s="13"/>
       <c r="K22" s="13"/>
       <c r="L22" s="13"/>
+      <c r="N22" s="13">
+        <f t="shared" si="4"/>
+        <v>20000</v>
+      </c>
+      <c r="O22" s="13">
+        <f t="shared" si="5"/>
+        <v>20210</v>
+      </c>
+      <c r="Q22" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:17" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1898</v>
       </c>
       <c r="B23" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1342210</v>
       </c>
       <c r="C23" s="5">
@@ -5702,15 +5952,15 @@
         <v>1352320</v>
       </c>
       <c r="D23" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>51700</v>
       </c>
       <c r="E23" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>31700</v>
       </c>
       <c r="F23" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>220</v>
       </c>
       <c r="G23" s="6">
@@ -5728,14 +5978,26 @@
       <c r="J23" s="13"/>
       <c r="K23" s="13"/>
       <c r="L23" s="13"/>
+      <c r="N23" s="13">
+        <f t="shared" si="4"/>
+        <v>20000</v>
+      </c>
+      <c r="O23" s="13">
+        <f t="shared" si="5"/>
+        <v>20220</v>
+      </c>
+      <c r="Q23" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:17" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1899</v>
       </c>
       <c r="B24" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1362430</v>
       </c>
       <c r="C24" s="5">
@@ -5743,15 +6005,15 @@
         <v>1372545</v>
       </c>
       <c r="D24" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>51800</v>
       </c>
       <c r="E24" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>31800</v>
       </c>
       <c r="F24" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>230</v>
       </c>
       <c r="G24" s="6">
@@ -5769,14 +6031,26 @@
       <c r="J24" s="13"/>
       <c r="K24" s="13"/>
       <c r="L24" s="13"/>
+      <c r="N24" s="13">
+        <f t="shared" si="4"/>
+        <v>20000</v>
+      </c>
+      <c r="O24" s="13">
+        <f t="shared" si="5"/>
+        <v>20230</v>
+      </c>
+      <c r="Q24" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:17" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1900</v>
       </c>
       <c r="B25" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1382660</v>
       </c>
       <c r="C25" s="5">
@@ -5784,15 +6058,15 @@
         <v>1392780</v>
       </c>
       <c r="D25" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>51900</v>
       </c>
       <c r="E25" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>31900</v>
       </c>
       <c r="F25" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>240</v>
       </c>
       <c r="G25" s="6">
@@ -5810,14 +6084,26 @@
       <c r="J25" s="13"/>
       <c r="K25" s="13"/>
       <c r="L25" s="13"/>
+      <c r="N25" s="13">
+        <f t="shared" si="4"/>
+        <v>20000</v>
+      </c>
+      <c r="O25" s="13">
+        <f t="shared" si="5"/>
+        <v>20240</v>
+      </c>
+      <c r="Q25" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:17" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1901</v>
       </c>
       <c r="B26" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1402900</v>
       </c>
       <c r="C26" s="5">
@@ -5825,15 +6111,15 @@
         <v>1413025</v>
       </c>
       <c r="D26" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>52000</v>
       </c>
       <c r="E26" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>32000</v>
       </c>
       <c r="F26" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>250</v>
       </c>
       <c r="G26" s="6">
@@ -5851,14 +6137,26 @@
       <c r="J26" s="13"/>
       <c r="K26" s="13"/>
       <c r="L26" s="13"/>
+      <c r="N26" s="13">
+        <f t="shared" si="4"/>
+        <v>20000</v>
+      </c>
+      <c r="O26" s="13">
+        <f t="shared" si="5"/>
+        <v>20250</v>
+      </c>
+      <c r="Q26" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="27" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:17" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1902</v>
       </c>
       <c r="B27" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1423150</v>
       </c>
       <c r="C27" s="5">
@@ -5866,15 +6164,15 @@
         <v>1433280</v>
       </c>
       <c r="D27" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>52100</v>
       </c>
       <c r="E27" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>32100</v>
       </c>
       <c r="F27" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>260</v>
       </c>
       <c r="G27" s="6">
@@ -5892,14 +6190,26 @@
       <c r="J27" s="13"/>
       <c r="K27" s="13"/>
       <c r="L27" s="13"/>
+      <c r="N27" s="13">
+        <f t="shared" si="4"/>
+        <v>20000</v>
+      </c>
+      <c r="O27" s="13">
+        <f t="shared" si="5"/>
+        <v>20260</v>
+      </c>
+      <c r="Q27" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="28" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:17" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1903</v>
       </c>
       <c r="B28" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1443410</v>
       </c>
       <c r="C28" s="5">
@@ -5907,15 +6217,15 @@
         <v>1453545</v>
       </c>
       <c r="D28" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>52200</v>
       </c>
       <c r="E28" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>32200</v>
       </c>
       <c r="F28" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>270</v>
       </c>
       <c r="G28" s="6">
@@ -5933,14 +6243,26 @@
       <c r="J28" s="13"/>
       <c r="K28" s="13"/>
       <c r="L28" s="13"/>
+      <c r="N28" s="13">
+        <f t="shared" si="4"/>
+        <v>20000</v>
+      </c>
+      <c r="O28" s="13">
+        <f t="shared" si="5"/>
+        <v>20270</v>
+      </c>
+      <c r="Q28" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:17" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1904</v>
       </c>
       <c r="B29" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1463680</v>
       </c>
       <c r="C29" s="5">
@@ -5948,15 +6270,15 @@
         <v>1473820</v>
       </c>
       <c r="D29" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>52300</v>
       </c>
       <c r="E29" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>32300</v>
       </c>
       <c r="F29" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>280</v>
       </c>
       <c r="G29" s="6">
@@ -5974,14 +6296,26 @@
       <c r="J29" s="13"/>
       <c r="K29" s="13"/>
       <c r="L29" s="13"/>
+      <c r="N29" s="13">
+        <f t="shared" si="4"/>
+        <v>20000</v>
+      </c>
+      <c r="O29" s="13">
+        <f t="shared" si="5"/>
+        <v>20280</v>
+      </c>
+      <c r="Q29" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:17" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1905</v>
       </c>
       <c r="B30" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1483960</v>
       </c>
       <c r="C30" s="5">
@@ -5989,15 +6323,15 @@
         <v>1494105</v>
       </c>
       <c r="D30" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>52400</v>
       </c>
       <c r="E30" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>32400</v>
       </c>
       <c r="F30" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>290</v>
       </c>
       <c r="G30" s="6">
@@ -6015,14 +6349,26 @@
       <c r="J30" s="13"/>
       <c r="K30" s="13"/>
       <c r="L30" s="13"/>
+      <c r="N30" s="13">
+        <f t="shared" si="4"/>
+        <v>20000</v>
+      </c>
+      <c r="O30" s="13">
+        <f t="shared" si="5"/>
+        <v>20290</v>
+      </c>
+      <c r="Q30" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:17" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1906</v>
       </c>
       <c r="B31" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1504250</v>
       </c>
       <c r="C31" s="5">
@@ -6030,15 +6376,15 @@
         <v>1514400</v>
       </c>
       <c r="D31" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>52500</v>
       </c>
       <c r="E31" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>32500</v>
       </c>
       <c r="F31" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>300</v>
       </c>
       <c r="G31" s="6">
@@ -6056,14 +6402,26 @@
       <c r="J31" s="13"/>
       <c r="K31" s="13"/>
       <c r="L31" s="13"/>
+      <c r="N31" s="13">
+        <f t="shared" si="4"/>
+        <v>20000</v>
+      </c>
+      <c r="O31" s="13">
+        <f t="shared" si="5"/>
+        <v>20300</v>
+      </c>
+      <c r="Q31" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:17" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1907</v>
       </c>
       <c r="B32" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1524550</v>
       </c>
       <c r="C32" s="5">
@@ -6071,15 +6429,15 @@
         <v>1534705</v>
       </c>
       <c r="D32" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>52600</v>
       </c>
       <c r="E32" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>32600</v>
       </c>
       <c r="F32" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>310</v>
       </c>
       <c r="G32" s="6">
@@ -6097,14 +6455,26 @@
       <c r="J32" s="13"/>
       <c r="K32" s="13"/>
       <c r="L32" s="13"/>
+      <c r="N32" s="13">
+        <f t="shared" si="4"/>
+        <v>20000</v>
+      </c>
+      <c r="O32" s="13">
+        <f t="shared" si="5"/>
+        <v>20310</v>
+      </c>
+      <c r="Q32" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:17" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1908</v>
       </c>
       <c r="B33" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1544860</v>
       </c>
       <c r="C33" s="5">
@@ -6112,15 +6482,15 @@
         <v>1555020</v>
       </c>
       <c r="D33" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>52700</v>
       </c>
       <c r="E33" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>32700</v>
       </c>
       <c r="F33" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>320</v>
       </c>
       <c r="G33" s="6">
@@ -6138,14 +6508,26 @@
       <c r="J33" s="13"/>
       <c r="K33" s="13"/>
       <c r="L33" s="13"/>
+      <c r="N33" s="13">
+        <f t="shared" si="4"/>
+        <v>20000</v>
+      </c>
+      <c r="O33" s="13">
+        <f t="shared" si="5"/>
+        <v>20320</v>
+      </c>
+      <c r="Q33" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="34" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:17" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1909</v>
       </c>
       <c r="B34" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1565180</v>
       </c>
       <c r="C34" s="5">
@@ -6153,15 +6535,15 @@
         <v>1575345</v>
       </c>
       <c r="D34" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>52800</v>
       </c>
       <c r="E34" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>32800</v>
       </c>
       <c r="F34" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>330</v>
       </c>
       <c r="G34" s="6">
@@ -6179,14 +6561,26 @@
       <c r="J34" s="13"/>
       <c r="K34" s="13"/>
       <c r="L34" s="13"/>
+      <c r="N34" s="13">
+        <f t="shared" si="4"/>
+        <v>20000</v>
+      </c>
+      <c r="O34" s="13">
+        <f t="shared" si="5"/>
+        <v>20330</v>
+      </c>
+      <c r="Q34" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:17" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1910</v>
       </c>
       <c r="B35" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1585510</v>
       </c>
       <c r="C35" s="5">
@@ -6194,15 +6588,15 @@
         <v>1595680</v>
       </c>
       <c r="D35" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>52900</v>
       </c>
       <c r="E35" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>32900</v>
       </c>
       <c r="F35" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>340</v>
       </c>
       <c r="G35" s="6">
@@ -6220,14 +6614,26 @@
       <c r="J35" s="13"/>
       <c r="K35" s="13"/>
       <c r="L35" s="13"/>
+      <c r="N35" s="13">
+        <f t="shared" si="4"/>
+        <v>20000</v>
+      </c>
+      <c r="O35" s="13">
+        <f t="shared" si="5"/>
+        <v>20340</v>
+      </c>
+      <c r="Q35" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="36" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:17" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1911</v>
       </c>
       <c r="B36" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1605850</v>
       </c>
       <c r="C36" s="5">
@@ -6235,15 +6641,15 @@
         <v>1616025</v>
       </c>
       <c r="D36" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>53000</v>
       </c>
       <c r="E36" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>33000</v>
       </c>
       <c r="F36" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>350</v>
       </c>
       <c r="G36" s="6">
@@ -6261,14 +6667,26 @@
       <c r="J36" s="13"/>
       <c r="K36" s="13"/>
       <c r="L36" s="13"/>
+      <c r="N36" s="13">
+        <f t="shared" si="4"/>
+        <v>20000</v>
+      </c>
+      <c r="O36" s="13">
+        <f t="shared" si="5"/>
+        <v>20350</v>
+      </c>
+      <c r="Q36" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="37" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:17" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1912</v>
       </c>
       <c r="B37" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1626200</v>
       </c>
       <c r="C37" s="5">
@@ -6276,15 +6694,15 @@
         <v>1636380</v>
       </c>
       <c r="D37" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>53100</v>
       </c>
       <c r="E37" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>33100</v>
       </c>
       <c r="F37" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>360</v>
       </c>
       <c r="G37" s="6">
@@ -6302,14 +6720,26 @@
       <c r="J37" s="13"/>
       <c r="K37" s="13"/>
       <c r="L37" s="13"/>
+      <c r="N37" s="13">
+        <f t="shared" si="4"/>
+        <v>20000</v>
+      </c>
+      <c r="O37" s="13">
+        <f t="shared" si="5"/>
+        <v>20360</v>
+      </c>
+      <c r="Q37" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="38" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:17" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>1913</v>
       </c>
       <c r="B38" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1646560</v>
       </c>
       <c r="C38" s="5">
@@ -6317,15 +6747,15 @@
         <v>1656745</v>
       </c>
       <c r="D38" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>53200</v>
       </c>
       <c r="E38" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>33200</v>
       </c>
       <c r="F38" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>370</v>
       </c>
       <c r="G38" s="6">
@@ -6343,14 +6773,26 @@
       <c r="J38" s="13"/>
       <c r="K38" s="13"/>
       <c r="L38" s="13"/>
+      <c r="N38" s="13">
+        <f t="shared" si="4"/>
+        <v>20000</v>
+      </c>
+      <c r="O38" s="13">
+        <f t="shared" si="5"/>
+        <v>20370</v>
+      </c>
+      <c r="Q38" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="39" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:17" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="3">
         <f>A38+1</f>
         <v>1914</v>
       </c>
       <c r="B39" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>1666930</v>
       </c>
       <c r="C39" s="5"/>
@@ -6364,7 +6806,7 @@
       <c r="K39" s="13"/>
       <c r="L39" s="13"/>
     </row>
-    <row r="40" spans="1:12" ht="15.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:17" ht="15.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="3"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -6378,7 +6820,7 @@
       <c r="K40" s="13"/>
       <c r="L40" s="13"/>
     </row>
-    <row r="41" spans="1:12" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="41" spans="1:17" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A41" s="10" t="s">
         <v>11</v>
       </c>
@@ -6420,8 +6862,16 @@
         <f t="array" ref="L41">SUM(L6+L6:L20)</f>
         <v>0</v>
       </c>
+      <c r="N41" s="11" cm="1">
+        <f t="array" ref="N41">SUM(N6+N6:N20)</f>
+        <v>600000</v>
+      </c>
+      <c r="O41" s="11" cm="1">
+        <f t="array" ref="O41">SUM(O6+O6:O20)</f>
+        <v>602550</v>
+      </c>
     </row>
-    <row r="42" spans="1:12" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="42" spans="1:17" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A42" s="10" t="s">
         <v>12</v>
       </c>
@@ -6463,8 +6913,16 @@
         <f>SUM(L21:L39)</f>
         <v>0</v>
       </c>
+      <c r="N42" s="11">
+        <f>SUM(N21:N39)</f>
+        <v>360000</v>
+      </c>
+      <c r="O42" s="11">
+        <f>SUM(O21:O39)</f>
+        <v>365130</v>
+      </c>
     </row>
-    <row r="43" spans="1:12" ht="15.6" x14ac:dyDescent="0.6">
+    <row r="43" spans="1:17" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A43" s="10" t="s">
         <v>13</v>
       </c>
@@ -6506,10 +6964,19 @@
         <f>L41+L42</f>
         <v>0</v>
       </c>
+      <c r="N43" s="11">
+        <f>N41+N42</f>
+        <v>960000</v>
+      </c>
+      <c r="O43" s="11">
+        <f>O41+O42</f>
+        <v>967680</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="B4:C4"/>
+    <mergeCell ref="N4:O4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/rtss-pre1917/src/main/resources/excel-templates/elementary-territory-1881-1913.xlsx
+++ b/rtss-pre1917/src/main/resources/excel-templates/elementary-territory-1881-1913.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\excel-templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD7041A1-247D-4708-ABE1-0BA194E2A85F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E158FE9F-5919-4AF1-8FC4-23CE167A98D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{BB18BFB1-C03A-41FE-BE1A-93D139757D6D}"/>
   </bookViews>
@@ -36,28 +36,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6826,17 +6804,17 @@
       </c>
       <c r="B41" s="10"/>
       <c r="C41" s="10"/>
-      <c r="D41" s="11" cm="1">
-        <f t="array" ref="D41">SUM(D6+D6:D20)</f>
-        <v>1510500</v>
-      </c>
-      <c r="E41" s="11" cm="1">
-        <f t="array" ref="E41">SUM(E6+E6:E20)</f>
-        <v>910500</v>
-      </c>
-      <c r="F41" s="11" cm="1">
-        <f t="array" ref="F41">SUM(F6+F6:F20)</f>
-        <v>2550</v>
+      <c r="D41" s="11">
+        <f>SUM(D6:D20)</f>
+        <v>760500</v>
+      </c>
+      <c r="E41" s="11">
+        <f t="shared" ref="E41:O41" si="12">SUM(E6:E20)</f>
+        <v>460500</v>
+      </c>
+      <c r="F41" s="11">
+        <f t="shared" si="12"/>
+        <v>1800</v>
       </c>
       <c r="G41" s="12">
         <f>AVERAGE(G6:G20)</f>
@@ -6850,25 +6828,25 @@
         <f>AVERAGE(I6:I20)</f>
         <v>17.480715361308548</v>
       </c>
-      <c r="J41" s="11" cm="1">
-        <f t="array" ref="J41">SUM(J6+J6:J20)</f>
+      <c r="J41" s="11">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="K41" s="11" cm="1">
-        <f t="array" ref="K41">SUM(K6+K6:K20)</f>
+      <c r="K41" s="11">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="L41" s="11" cm="1">
-        <f t="array" ref="L41">SUM(L6+L6:L20)</f>
+      <c r="L41" s="11">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="N41" s="11" cm="1">
-        <f t="array" ref="N41">SUM(N6+N6:N20)</f>
-        <v>600000</v>
-      </c>
-      <c r="O41" s="11" cm="1">
-        <f t="array" ref="O41">SUM(O6+O6:O20)</f>
-        <v>602550</v>
+      <c r="N41" s="11">
+        <f t="shared" si="12"/>
+        <v>300000</v>
+      </c>
+      <c r="O41" s="11">
+        <f t="shared" si="12"/>
+        <v>301800</v>
       </c>
     </row>
     <row r="42" spans="1:17" ht="15.6" x14ac:dyDescent="0.6">
@@ -6930,15 +6908,15 @@
       <c r="C43" s="10"/>
       <c r="D43" s="11">
         <f>D41+D42</f>
-        <v>2452800</v>
+        <v>1702800</v>
       </c>
       <c r="E43" s="11">
         <f>E41+E42</f>
-        <v>1492800</v>
+        <v>1042800</v>
       </c>
       <c r="F43" s="11">
         <f>F41+F42</f>
-        <v>7680</v>
+        <v>6930</v>
       </c>
       <c r="G43" s="12">
         <f>AVERAGE(G6:G38)</f>
@@ -6966,11 +6944,11 @@
       </c>
       <c r="N43" s="11">
         <f>N41+N42</f>
-        <v>960000</v>
+        <v>660000</v>
       </c>
       <c r="O43" s="11">
         <f>O41+O42</f>
-        <v>967680</v>
+        <v>666930</v>
       </c>
     </row>
   </sheetData>
